--- a/stories/arbres/ATOM-SEC.MAI.001-05.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Damien joue dans la salle à manger. Il a des trains en bois. Les trains sont lisses. Papa plie les serviettes. Damien veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Damien appelle papa. Il dit : papa, la lumière. Papa vient. Papa allume la lampe. La pièce est claire. Maman entre. Maman dit : on appelle un adulte. On appelle papa ou maman. Les mains restent avec les jouets. Damien reprend un train. Il fait un pont. Papa dit : les prises sont pour les adultes. Damien tient les jouets. Les mains sont avec les trains.</t>
+          <t>Damien joue dans la salle à manger. Il a des trains en bois. Les trains sont lisses. Papa plie les serviettes. Damien veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Damien appelle papa. Papa, la lumière. Papa vient. Papa allume la lampe. La pièce est claire. Maman entre. On appelle un adulte. On appelle papa ou maman. Les mains restent avec les jouets. Damien reprend un train. Il fait un pont. Les prises sont pour les adultes. Damien tient les jouets. Les mains sont avec les trains.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Damien joue dans la salle à manger. Il a des trains en bois. Les trains sont lisses. Papa plie les serviettes. Damien veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Damien appelle papa.
+narrateur|Papa, la lumière. Papa vient. Papa allume la lampe.
+narrateur|La pièce est claire. Maman entre.
+maman|On appelle un adulte. On appelle papa ou maman.
+narrateur|Les mains restent avec les jouets. Damien reprend un train. Il fait un pont.
+papa|Les prises sont pour les adultes.
+narrateur|Damien tient les jouets. Les mains sont avec les trains.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1496,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Damien veut la lumière. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1673,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Damien a appelé un adulte. Les mains étaient avec les jouets. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1803,6 +1840,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Damien pousse un train. La lumière reste allumée.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1965,6 +2007,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1983,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2000,6 +2047,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.001-05.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Damien tient les jouets. Les mains sont avec les trains.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1503,6 +1509,7 @@
           <t>narrateur|Damien veut la lumière. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1678,6 +1685,7 @@
           <t>narrateur|Damien a appelé un adulte. Les mains étaient avec les jouets. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1845,6 +1853,7 @@
           <t>narrateur|Damien pousse un train. La lumière reste allumée.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2012,6 +2021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2054,6 +2064,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2255,6 +2279,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.MAI.001-05.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Damien appelle pour la lampe</t>
+          <t>Le pont de trains de Nino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La pluie tapote la vitre. Nino construit un pont de trains. Il appelle papa pour la lumière. Les mains restent avec les jouets.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Damien joue dans la salle à manger. Il a des trains en bois. Les trains sont lisses. Papa plie les serviettes. Damien veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Damien appelle papa. Papa, la lumière. Papa vient. Papa allume la lampe. La pièce est claire. Maman entre. On appelle un adulte. On appelle papa ou maman. Les mains restent avec les jouets. Damien reprend un train. Il fait un pont. Les prises sont pour les adultes. Damien tient les jouets. Les mains sont avec les trains.</t>
+          <t>La pluie tapote la vitre de la salle à manger. Les gouttes font des petits ronds. La nappe a des rayures jaunes. Ça sent la soupe tiède. Les serviettes sont pliées en carrés. Nino, tu as vu la pluie ? Oui, papa. Elle chante. Elle chante sur le toit. Les serviettes sont prêtes. Merci. Une gouttière chante dehors. Le village est tout mouillé. Tu as entendu la gouttière ? Oui. Elle chante aussi. En ce moment, Nino est au tapis. Le tapis est doux et bleu. Les trains en bois sont lisses. Un wagon rouge attend. Un wagon jaune attend aussi. Je fais un pont, papa. Un beau pont. Nino pousse le wagon rouge. Le bois fait un petit bruit. Il pose le wagon jaune. Tes mains sont avec les trains ? Oui, maman. Bravo. La pièce est un peu sombre. Nino veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Nino appelle un adulte. Papa, la lumière. J'arrive, Nino. Papa vient près du tapis. Je m'occupe de la lumière. Papa allume la lampe. La pièce est claire. Le pont de bois brille. Tu as appelé un adulte. On appelle papa ou maman. Bravo, Nino. Les prises sont pour les adultes. Les mains restent avec les jouets. Nino reprend un train. Il fait un pont plus long. Le pont est long. Oui. Tes mains sont avec les trains. Tu as fait du bon travail. Nino tient les jouets. Les mains sont avec les trains. La pluie chante encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,60 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Damien joue dans la salle à manger. Il a des trains en bois. Les trains sont lisses. Papa plie les serviettes. Damien veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Damien appelle papa.
-narrateur|Papa, la lumière. Papa vient. Papa allume la lampe.
-narrateur|La pièce est claire. Maman entre.
-maman|On appelle un adulte. On appelle papa ou maman.
-narrateur|Les mains restent avec les jouets. Damien reprend un train. Il fait un pont.
+          <t>narrateur|La pluie tapote la vitre de la salle à manger.
+narrateur|Les gouttes font des petits ronds.
+narrateur|La nappe a des rayures jaunes.
+narrateur|Ça sent la soupe tiède.
+narrateur|Les serviettes sont pliées en carrés.
+papa|Nino, tu as vu la pluie ?
+enfant-m|Oui, papa. Elle chante.
+papa|Elle chante sur le toit.
+maman|Les serviettes sont prêtes.
+papa|Merci.
+narrateur|Une gouttière chante dehors.
+narrateur|Le village est tout mouillé.
+maman|Tu as entendu la gouttière ?
+enfant-m|Oui. Elle chante aussi.
+narrateur|En ce moment, Nino est au tapis.
+narrateur|Le tapis est doux et bleu.
+narrateur|Les trains en bois sont lisses.
+narrateur|Un wagon rouge attend.
+narrateur|Un wagon jaune attend aussi.
+enfant-m|Je fais un pont, papa.
+papa|Un beau pont.
+narrateur|Nino pousse le wagon rouge.
+narrateur|Le bois fait un petit bruit.
+narrateur|Il pose le wagon jaune.
+maman|Tes mains sont avec les trains ?
+enfant-m|Oui, maman.
+maman|Bravo.
+narrateur|La pièce est un peu sombre.
+narrateur|Nino veut plus de lumière.
+narrateur|Il regarde ses mains.
+narrateur|Les mains restent avec les jouets.
+narrateur|Nino appelle un adulte.
+enfant-m|Papa, la lumière.
+papa|J'arrive, Nino.
+narrateur|Papa vient près du tapis.
+papa|Je m'occupe de la lumière.
+narrateur|Papa allume la lampe.
+narrateur|La pièce est claire.
+narrateur|Le pont de bois brille.
+maman|Tu as appelé un adulte.
+maman|On appelle papa ou maman.
+papa|Bravo, Nino.
 papa|Les prises sont pour les adultes.
-narrateur|Damien tient les jouets. Les mains sont avec les trains.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+narrateur|Les mains restent avec les jouets.
+narrateur|Nino reprend un train.
+narrateur|Il fait un pont plus long.
+enfant-m|Le pont est long.
+papa|Oui. Tes mains sont avec les trains.
+maman|Tu as fait du bon travail.
+narrateur|Nino tient les jouets.
+narrateur|Les mains sont avec les trains.
+narrateur|La pluie chante encore.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1402,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Damien veut la lumière. Que fait-il ?</t>
+          <t>Nino veut la lumière. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,10 +1562,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Damien veut la lumière. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nino veut la lumière.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1534,7 +1590,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Damien a appelé un adulte. Les mains étaient avec les jouets. Papa et maman sont là.</t>
+          <t>Nino a appelé un adulte. Les mains étaient avec les jouets. Tu as appelé papa ? Oui. Bravo. On appelle papa ou maman. Le wagon rouge est sur le pont. La nappe a toujours ses rayures. Ça sent encore la soupe. Tes mains sont avec les jouets ? Oui, maman. Bravo.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1682,10 +1738,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Damien a appelé un adulte. Les mains étaient avec les jouets. Papa et maman sont là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nino a appelé un adulte.
+narrateur|Les mains étaient avec les jouets.
+papa|Tu as appelé papa ?
+enfant-m|Oui.
+papa|Bravo.
+maman|On appelle papa ou maman.
+narrateur|Le wagon rouge est sur le pont.
+narrateur|La nappe a toujours ses rayures.
+narrateur|Ça sent encore la soupe.
+maman|Tes mains sont avec les jouets ?
+enfant-m|Oui, maman.
+maman|Bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1710,7 +1776,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Damien pousse un train. La lumière reste allumée.</t>
+          <t>Nino pousse un train. Le bois est lisse. La lumière reste allumée. Le pont est fini ? Oui, papa. Bravo. Tu as fait du bon travail. On va manger la soupe ? Oui, maman. La pluie tapote encore la vitre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1850,10 +1916,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Damien pousse un train. La lumière reste allumée.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Nino pousse un train.
+narrateur|Le bois est lisse.
+narrateur|La lumière reste allumée.
+papa|Le pont est fini ?
+enfant-m|Oui, papa.
+papa|Bravo. Tu as fait du bon travail.
+maman|On va manger la soupe ?
+enfant-m|Oui, maman.
+narrateur|La pluie tapote encore la vitre.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1878,7 +1951,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a fait un pont. Il a appelé papa. Les mains étaient avec les trains. Bravo, Nino. La lumière est là. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2018,10 +2091,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Nino a fait un pont.
+narrateur|Il a appelé papa.
+narrateur|Les mains étaient avec les trains.
+papa|Bravo, Nino.
+maman|La lumière est là.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2040,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2078,6 +2155,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.001-05.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.001-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La pluie tapote la vitre de la salle à manger. Les gouttes font des petits ronds. La nappe a des rayures jaunes. Ça sent la soupe tiède. Les serviettes sont pliées en carrés. Nino, tu as vu la pluie ? Oui, papa. Elle chante. Elle chante sur le toit. Les serviettes sont prêtes. Merci. Une gouttière chante dehors. Le village est tout mouillé. Tu as entendu la gouttière ? Oui. Elle chante aussi. En ce moment, Nino est au tapis. Le tapis est doux et bleu. Les trains en bois sont lisses. Un wagon rouge attend. Un wagon jaune attend aussi. Je fais un pont, papa. Un beau pont. Nino pousse le wagon rouge. Le bois fait un petit bruit. Il pose le wagon jaune. Tes mains sont avec les trains ? Oui, maman. Bravo. La pièce est un peu sombre. Nino veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Nino appelle un adulte. Papa, la lumière. J'arrive, Nino. Papa vient près du tapis. Je m'occupe de la lumière. Papa allume la lampe. La pièce est claire. Le pont de bois brille. Tu as appelé un adulte. On appelle papa ou maman. Bravo, Nino. Les prises sont pour les adultes. Les mains restent avec les jouets. Nino reprend un train. Il fait un pont plus long. Le pont est long. Oui. Tes mains sont avec les trains. Tu as fait du bon travail. Nino tient les jouets. Les mains sont avec les trains. La pluie chante encore.</t>
+          <t>La pluie tapote la vitre de la salle à manger. Les gouttes font des petits ronds. La nappe a des rayures jaunes. Ça sent la soupe tiède. Les serviettes sont pliées en carrés. Nino, tu as vu la pluie ? Oui, papa. Elle chante. Elle chante sur le toit. Les serviettes sont prêtes. Merci. Une gouttière chante dehors. Le village est tout mouillé. Tu as entendu la gouttière ? Oui. Elle chante aussi. En ce moment, Nino est au tapis. Le tapis est doux et bleu. Les trains en bois sont lisses. Un wagon rouge attend. Un wagon jaune attend aussi. Je fais un pont, papa. Un beau pont. Nino pousse le wagon rouge. Le bois fait un petit bruit. Il pose le wagon jaune. Tes mains sont avec les trains ? Oui, maman. Bravo. La pièce est un peu sombre. Nino veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Nino appelle un adulte. Papa, la lumière. J'arrive, Nino. Papa vient près du tapis. Je m'occupe de la lumière. Papa allume la lampe. La pièce est claire. Le pont de bois brille. Tu as appelé un adulte. On appelle papa ou maman. Bravo, Nino. Les prises sont pour les adultes. Les mains restent avec les jouets. Nino reprend un train. Il fait un pont plus long. Le pont est long. Oui. Tes mains sont avec les trains. Nino tient les jouets. Les mains sont avec les trains. La pluie chante encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Damien joue dans la salle à manger. Il a des trains en bois. Les trains sont lisses. Papa plie les serviettes. Damien veut plus de lumière. Il regarde ses &lt;emphasis level="moderate"&gt;mains&lt;/emphasis&gt;. Les mains restent avec les jouets. Damien appelle papa. Il dit : papa, la lumière. Papa vient. Papa allume la lampe. La pièce est claire. Maman entre. Maman dit : on appelle un adulte. On appelle papa ou maman. Les mains restent avec les jouets. Damien reprend un train. Il fait un pont. Papa dit : les prises sont pour les adultes. Damien tient les jouets. Les mains sont avec les trains.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La pluie tapote la vitre de la salle à manger. Les gouttes font des petits ronds. La nappe a des rayures jaunes. Ça sent la soupe tiède. Les serviettes sont pliées en carrés. Nino, tu as vu la pluie ? Oui, papa. Elle chante. Elle chante sur le toit. Les serviettes sont prêtes. Merci. Une gouttière chante dehors. Le village est tout mouillé. Tu as entendu la gouttière ? Oui. Elle chante aussi. En ce moment, Nino est au tapis. Le tapis est doux et bleu. Les trains en bois sont lisses. Un wagon rouge attend. Un wagon jaune attend aussi. Je fais un pont, papa. Un beau pont. Nino pousse le wagon rouge. Le bois fait un petit bruit. Il pose le wagon jaune. Tes mains sont avec les trains ? Oui, maman. Bravo. La pièce est un peu sombre. Nino veut plus de lumière. Il regarde ses mains. Les mains restent avec les jouets. Nino appelle un adulte. Papa, la lumière. J'arrive, Nino. Papa vient près du tapis. Je m'occupe de la lumière. Papa allume la lampe. La pièce est claire. Le pont de bois brille. Tu as appelé un adulte. On appelle papa ou maman. Bravo, Nino. Les prises sont pour les adultes. Les mains restent avec les jouets. Nino reprend un train. Il fait un pont plus long. Le pont est long. Oui. Tes mains sont avec les trains. Nino tient les jouets. Les mains sont avec les trains. La pluie chante encore.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1372,7 +1372,6 @@
 narrateur|Il fait un pont plus long.
 enfant-m|Le pont est long.
 papa|Oui. Tes mains sont avec les trains.
-maman|Tu as fait du bon travail.
 narrateur|Nino tient les jouets.
 narrateur|Les mains sont avec les trains.
 narrateur|La pluie chante encore.</t>
@@ -1407,7 +1406,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Damien veut la lumière. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino veut la lumière. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1595,7 +1594,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Damien a appelé un adulte. Les &lt;emphasis level="moderate"&gt;mains&lt;/emphasis&gt; étaient avec les jouets. Papa et maman sont là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a appelé un adulte. Les mains étaient avec les jouets. Tu as appelé papa ? Oui. Bravo. On appelle papa ou maman. Le wagon rouge est sur le pont. La nappe a toujours ses rayures. Ça sent encore la soupe. Tes mains sont avec les jouets ? Oui, maman. Bravo.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1776,12 +1775,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nino pousse un train. Le bois est lisse. La lumière reste allumée. Le pont est fini ? Oui, papa. Bravo. Tu as fait du bon travail. On va manger la soupe ? Oui, maman. La pluie tapote encore la vitre.</t>
+          <t>Nino pousse un train. Le bois est lisse. La lumière reste allumée. Le pont est fini ? Oui, papa. On va manger la soupe ? Oui, maman. La pluie tapote encore la vitre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Damien pousse un train. La lumière reste allumée.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino pousse un train. Le bois est lisse. La lumière reste allumée. Le pont est fini ? Oui, papa. On va manger la soupe ? Oui, maman. La pluie tapote encore la vitre.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1921,7 +1920,6 @@
 narrateur|La lumière reste allumée.
 papa|Le pont est fini ?
 enfant-m|Oui, papa.
-papa|Bravo. Tu as fait du bon travail.
 maman|On va manger la soupe ?
 enfant-m|Oui, maman.
 narrateur|La pluie tapote encore la vitre.</t>
@@ -1951,12 +1949,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Nino a fait un pont. Il a appelé papa. Les mains étaient avec les trains. Bravo, Nino. La lumière est là. L'histoire est finie.</t>
+          <t>Nino a fait un pont. Il a appelé papa. Les mains étaient avec les trains. Bravo, Nino. La lumière est là.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a fait un pont. Il a appelé papa. Les mains étaient avec les trains. Bravo, Nino. La lumière est là.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2095,8 +2093,7 @@
 narrateur|Il a appelé papa.
 narrateur|Les mains étaient avec les trains.
 papa|Bravo, Nino.
-maman|La lumière est là.
-narrateur|L'histoire est finie.</t>
+maman|La lumière est là.</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2162,6 +2159,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.001-05.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.001-05.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Damien, papa, maman</t>
+          <t>Nino, papa, maman</t>
         </is>
       </c>
     </row>
